--- a/artfynd/A 48052-2022 artfynd.xlsx
+++ b/artfynd/A 48052-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 48052-2022 artfynd.xlsx
+++ b/artfynd/A 48052-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>69300225</v>
+        <v>69300227</v>
       </c>
       <c r="B2" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>546859.197070547</v>
+        <v>546933</v>
       </c>
       <c r="R2" t="n">
-        <v>7009461.046733268</v>
+        <v>7009470</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,21 +743,11 @@
           <t>2017-06-15</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2017-06-15</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -779,12 +764,12 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>glasbjörk</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Betula pubescens</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AN2" t="n">
@@ -792,7 +777,7 @@
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>1 substratenheter # Senvuxen björk # Betula pubescens</t>
+          <t>1 substratenheter # Klen, murken granlåga # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -810,15 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>69300221</v>
+        <v>102143554</v>
       </c>
       <c r="B3" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101299</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -826,34 +806,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6462</v>
+        <v>1365</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Överammer, Jmt</t>
+          <t>Slåttmyrkojan, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>546708.0701625078</v>
+        <v>546848</v>
       </c>
       <c r="R3" t="n">
-        <v>7009476.90270559</v>
+        <v>7009299</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -880,22 +860,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2017-06-15</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-07-03</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2017-06-15</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-07-03</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -906,54 +876,26 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Gransumpskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AN3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>1 substratenheter # Död sälg # Salix caprea</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Louise Almén</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Louise Almén</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>69300227</v>
+        <v>69300222</v>
       </c>
       <c r="B4" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -961,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -985,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>546933.1633255264</v>
+        <v>546708</v>
       </c>
       <c r="R4" t="n">
-        <v>7009469.791475341</v>
+        <v>7009477</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1018,21 +960,11 @@
           <t>2017-06-15</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2017-06-15</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1049,12 +981,12 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AN4" t="n">
@@ -1062,7 +994,7 @@
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>1 substratenheter # Klen, murken granlåga # Picea abies</t>
+          <t>1 substratenheter # Död sälg # Salix caprea</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1080,15 +1012,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>69300222</v>
+        <v>69300225</v>
       </c>
       <c r="B5" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1120,10 +1047,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>546708.0701625078</v>
+        <v>546859</v>
       </c>
       <c r="R5" t="n">
-        <v>7009476.90270559</v>
+        <v>7009461</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1153,21 +1080,11 @@
           <t>2017-06-15</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2017-06-15</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1184,12 +1101,12 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>glasbjörk</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Betula pubescens</t>
         </is>
       </c>
       <c r="AN5" t="n">
@@ -1197,7 +1114,7 @@
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>1 substratenheter # Död sälg # Salix caprea</t>
+          <t>1 substratenheter # Senvuxen björk # Betula pubescens</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1212,6 +1129,126 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>69300221</v>
+      </c>
+      <c r="B6" t="n">
+        <v>80461</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Överammer, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>546708</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7009477</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2017-06-15</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2017-06-15</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Gransumpskog</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AN6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>1 substratenheter # Död sälg # Salix caprea</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 48052-2022 artfynd.xlsx
+++ b/artfynd/A 48052-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -792,6 +797,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69300227</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -889,6 +899,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102143554</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1009,6 +1024,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69300222</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1129,6 +1149,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69300225</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1249,8 +1274,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69300221</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>